--- a/3DGS_Part/3_Experiment/3DGS_QE.xlsx
+++ b/3DGS_Part/3_Experiment/3DGS_QE.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yhlee/Desktop/2_Research/2_Writing/6_방미공하계학술대회'26/KNUVI_Capstone_Project_2026-1/3DGS_Part/3_Experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AA9CE3-750C-564E-86AF-180CD99FECC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51103997-7F8D-6048-8B9E-847B77D49DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="17340" xr2:uid="{5E6B10C3-38D1-E645-9B79-919990FD38AC}"/>
+    <workbookView xWindow="-4460" yWindow="-21000" windowWidth="38400" windowHeight="21000" xr2:uid="{5E6B10C3-38D1-E645-9B79-919990FD38AC}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="By_weathered" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="21">
   <si>
     <t>Scene</t>
   </si>
@@ -78,6 +78,27 @@
   </si>
   <si>
     <t>hydrant</t>
+  </si>
+  <si>
+    <t>pillar</t>
+  </si>
+  <si>
+    <t>road</t>
+  </si>
+  <si>
+    <t>sky</t>
+  </si>
+  <si>
+    <t>stair</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>by original</t>
+  </si>
+  <si>
+    <t>by weathered (Input)</t>
   </si>
 </sst>
 </file>
@@ -99,20 +120,20 @@
       <scheme val="major"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="14"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Display"/>
       <scheme val="major"/>
@@ -138,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -146,13 +167,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -488,472 +515,1112 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA87D6C-C6D9-3841-B04B-5DF823BA118C}">
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21A23D0C-5B50-C44D-9488-1885989BB4C4}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="G2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1">
-        <v>19.861000000000001</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.313</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.58199999999999996</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="4"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1">
-        <v>19.145</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.27300000000000002</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.66700000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4"/>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
+        <v>18.939</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="5">
+        <v>18.347000000000001</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0.42699999999999999</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4"/>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="5">
+        <v>21.99</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4"/>
+      <c r="C20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5">
+        <v>21.69</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4"/>
+      <c r="C24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4"/>
+      <c r="C26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4"/>
+      <c r="C28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="4"/>
+      <c r="B29" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4"/>
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="4"/>
+      <c r="B31" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="4"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4"/>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4"/>
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="5">
+        <v>19.353999999999999</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="F35" s="5">
+        <v>0.40600000000000003</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4"/>
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="4"/>
+      <c r="B39" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="4"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="5">
+        <v>19.495000000000001</v>
+      </c>
+      <c r="E39" s="5">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="F39" s="5">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4"/>
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4"/>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="4"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="5">
+        <v>21.536000000000001</v>
+      </c>
+      <c r="E43" s="5">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="F43" s="5">
+        <v>0.376</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4"/>
+      <c r="C44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="4"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4"/>
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="4"/>
+      <c r="B47" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="4"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="5">
+        <v>20.512</v>
+      </c>
+      <c r="E47" s="5">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="F47" s="5">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="4"/>
+      <c r="C48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="4"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="5" t="s">
-        <v>7</v>
+      <c r="C49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A34:A41"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="A42:A49"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="A18:A25"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A2:A9"/>
-    <mergeCell ref="A10:A17"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
+  <mergeCells count="32">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="A35:A42"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="A43:A50"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A19:A26"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A3:A10"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A11:A18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B17:B18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
